--- a/mobile/src/ElectronicLogbook.Mobile/Templates/LogbookExportCompact.xlsx
+++ b/mobile/src/ElectronicLogbook.Mobile/Templates/LogbookExportCompact.xlsx
@@ -892,87 +892,63 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+  <cellXfs count="120">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0"/>
+    <xf numFmtId="172" fontId="3" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="4" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -980,59 +956,59 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1055,7 +1031,7 @@
     <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1066,9 +1042,6 @@
     </xf>
     <xf numFmtId="170" fontId="6" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="172" fontId="8" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1088,13 +1061,13 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1109,17 +1082,6 @@
     <xf numFmtId="165" fontId="8" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1132,28 +1094,6 @@
     <xf numFmtId="166" fontId="7" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1268,9 +1208,80 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="172" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="119">
     <dxf>
@@ -1297,6 +1308,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1311,6 +1323,33 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1335,6 +1374,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1349,6 +1389,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1373,6 +1442,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1387,6 +1457,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1411,6 +1510,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1425,6 +1525,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1449,6 +1578,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1463,6 +1593,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1487,7 +1646,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1502,6 +1661,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1526,6 +1714,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1540,6 +1729,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1564,6 +1782,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1578,6 +1797,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1602,6 +1850,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1616,6 +1865,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1640,6 +1918,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1654,6 +1933,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1678,6 +1986,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1692,6 +2001,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1716,6 +2054,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1730,6 +2069,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1754,6 +2122,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1768,6 +2137,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1792,6 +2190,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1806,6 +2205,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1830,6 +2258,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1844,6 +2273,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1869,7 +2327,7 @@
           <bgColor rgb="FF333333"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1884,6 +2342,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="169" formatCode="0;;;@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1928,25 +2415,17 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="165" formatCode="0.0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1955,13 +2434,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2008,26 +2484,17 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2035,13 +2502,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2088,26 +2552,17 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2115,13 +2570,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2168,26 +2620,17 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2195,13 +2638,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2248,6 +2688,34 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -2282,6 +2750,306 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2328,26 +3096,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2355,13 +3115,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2408,26 +3165,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2435,13 +3184,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2488,26 +3234,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2515,13 +3253,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2568,26 +3303,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2595,13 +3322,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2648,26 +3372,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2675,13 +3391,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2728,26 +3441,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2755,13 +3460,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2808,26 +3510,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2835,13 +3529,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2888,6 +3579,35 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -2922,6 +3642,518 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2968,26 +4200,18 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF333333"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2995,13 +4219,10 @@
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3048,6 +4269,35 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -3082,6 +4332,104 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF333333"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3122,6 +4470,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -3153,6 +4531,34 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3186,6 +4592,34 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3217,6 +4651,36 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3262,6 +4726,34 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -3293,6 +4785,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="dd"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3339,6 +4860,35 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="d"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -3373,6 +4923,35 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="mmm"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3419,6 +4998,39 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -3453,6 +5065,41 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="172" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3477,6 +5124,7 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -3505,1628 +5153,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="169" formatCode="0;;;@"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="dd"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="d"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="mmm"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="172" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
@@ -5269,99 +5296,99 @@
     <sortCondition ref="C6"/>
   </sortState>
   <tableColumns count="57">
-    <tableColumn id="56" xr3:uid="{D480B3D9-F0FD-4EFA-B700-B58C42026787}" name="EntryID" dataDxfId="113" totalsRowDxfId="56"/>
-    <tableColumn id="1" xr3:uid="{4A9F7973-DB93-445C-A438-9DA51DE4C8E6}" name="Date" dataDxfId="112" totalsRowDxfId="55">
+    <tableColumn id="56" xr3:uid="{D480B3D9-F0FD-4EFA-B700-B58C42026787}" name="EntryID" dataDxfId="113" totalsRowDxfId="112"/>
+    <tableColumn id="1" xr3:uid="{4A9F7973-DB93-445C-A438-9DA51DE4C8E6}" name="Date" dataDxfId="111" totalsRowDxfId="110">
       <calculatedColumnFormula>IFERROR(IF(DAY(DATE(Logbook[[#This Row],[Year]],IF(ISNUMBER(Logbook[[#This Row],[Month]]),MONTH(Logbook[[#This Row],[Month]]),MONTH(DATEVALUE(Logbook[[#This Row],[Month]]&amp;" 1"))),IF(ISNUMBER(Logbook[[#This Row],[Day]]),IF(Logbook[[#This Row],[Day]]&gt;31,DAY(Logbook[[#This Row],[Day]]),Logbook[[#This Row],[Day]]),VALUE(Logbook[[#This Row],[Day]]))))&lt;&gt;IF(ISNUMBER(Logbook[[#This Row],[Day]]),IF(Logbook[[#This Row],[Day]]&gt;31,DAY(Logbook[[#This Row],[Day]]),Logbook[[#This Row],[Day]]),VALUE(Logbook[[#This Row],[Day]])),NA(),DATE(Logbook[[#This Row],[Year]],IF(ISNUMBER(Logbook[[#This Row],[Month]]),MONTH(Logbook[[#This Row],[Month]]),MONTH(DATEVALUE(Logbook[[#This Row],[Month]]&amp;" 1"))),IF(ISNUMBER(Logbook[[#This Row],[Day]]),IF(Logbook[[#This Row],[Day]]&gt;31,DAY(Logbook[[#This Row],[Day]]),Logbook[[#This Row],[Day]]),VALUE(Logbook[[#This Row],[Day]])))),NA())</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="53" xr3:uid="{5DE4E2FA-DD37-47CC-B3B2-F1F7CE60F8EF}" name="Year" dataDxfId="111" totalsRowDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{7F2FD0DE-1EBD-4A25-9AB2-8B2FD2016437}" name="Month" dataDxfId="110" totalsRowDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{C1637A1C-51D7-4EF1-B132-362CD3F92571}" name="Day" dataDxfId="109" totalsRowDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{96485EE2-5F0F-4FA0-B939-E32C66C44C7A}" name="Type" dataDxfId="108" totalsRowDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{4F0FBA5D-D369-4B9F-89AE-FEDEFC370AFE}" name="Reg" dataDxfId="107" totalsRowDxfId="50"/>
-    <tableColumn id="59" xr3:uid="{08CD5548-8146-40A6-94B9-0F79712B2ABF}" name="Flight ID" dataDxfId="106" totalsRowDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{0E4DB6A7-0018-4A8F-AFD7-61529B568497}" name="PIC" totalsRowLabel="Grand Total Flying Hours" dataDxfId="105" totalsRowDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{7D9307E7-1F1E-42B0-9A4E-D7903D4B651E}" name="Other Pilot or Crew" totalsRowFunction="custom" dataDxfId="104" totalsRowDxfId="47">
+    <tableColumn id="53" xr3:uid="{5DE4E2FA-DD37-47CC-B3B2-F1F7CE60F8EF}" name="Year" dataDxfId="109" totalsRowDxfId="108"/>
+    <tableColumn id="2" xr3:uid="{7F2FD0DE-1EBD-4A25-9AB2-8B2FD2016437}" name="Month" dataDxfId="107" totalsRowDxfId="106"/>
+    <tableColumn id="3" xr3:uid="{C1637A1C-51D7-4EF1-B132-362CD3F92571}" name="Day" dataDxfId="105" totalsRowDxfId="104"/>
+    <tableColumn id="4" xr3:uid="{96485EE2-5F0F-4FA0-B939-E32C66C44C7A}" name="Type" dataDxfId="103" totalsRowDxfId="102"/>
+    <tableColumn id="5" xr3:uid="{4F0FBA5D-D369-4B9F-89AE-FEDEFC370AFE}" name="Reg" dataDxfId="101" totalsRowDxfId="100"/>
+    <tableColumn id="59" xr3:uid="{08CD5548-8146-40A6-94B9-0F79712B2ABF}" name="Flight ID" dataDxfId="99" totalsRowDxfId="98"/>
+    <tableColumn id="6" xr3:uid="{0E4DB6A7-0018-4A8F-AFD7-61529B568497}" name="PIC" totalsRowLabel="Grand Total Flying Hours" dataDxfId="97" totalsRowDxfId="96"/>
+    <tableColumn id="7" xr3:uid="{7D9307E7-1F1E-42B0-9A4E-D7903D4B651E}" name="Other Pilot or Crew" totalsRowFunction="custom" dataDxfId="95" totalsRowDxfId="94">
       <totalsRowFormula>SUBTOTAL(109,Logbook[TotalHours])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="62" xr3:uid="{35D88777-AA03-4EF0-B227-9E2048B1AA5E}" name="Details" dataDxfId="103" totalsRowDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{C53B3FE9-B5B3-4FE4-9D2F-CC5CB5F157FB}" name="Custom 1" totalsRowFunction="sum" dataDxfId="102" totalsRowDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{D4DF1EA3-5D43-434F-AEBE-A605D9FFD457}" name="Custom 2" totalsRowFunction="sum" dataDxfId="101" totalsRowDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{741C7510-6E1A-49A3-9C9E-E42097510CEC}" name="Custom 3" totalsRowFunction="sum" dataDxfId="100" totalsRowDxfId="43"/>
-    <tableColumn id="57" xr3:uid="{4E4B2A2B-F980-49E5-9F31-D9E96FB9A587}" name="Custom 4" totalsRowFunction="sum" dataDxfId="99" totalsRowDxfId="42"/>
-    <tableColumn id="12" xr3:uid="{EC4A1A18-0A2D-49AC-BFCD-E01030F64888}" name="SeIcusDay" totalsRowFunction="sum" dataDxfId="98" totalsRowDxfId="41"/>
-    <tableColumn id="13" xr3:uid="{40EA09A9-61CC-4653-B74B-0553995DCA63}" name="SeIcusNight" totalsRowFunction="sum" dataDxfId="97" totalsRowDxfId="40"/>
-    <tableColumn id="14" xr3:uid="{482A4ED7-9580-4817-A603-06ECE9BF848E}" name="SeDualDay" totalsRowFunction="sum" dataDxfId="96" totalsRowDxfId="39"/>
-    <tableColumn id="15" xr3:uid="{ECD3AC03-3033-4736-ACF4-108BA4CADCA9}" name="SeDualNight" totalsRowFunction="sum" dataDxfId="95" totalsRowDxfId="38"/>
-    <tableColumn id="16" xr3:uid="{0D5B8F94-E65D-4CF8-BCFB-AB7B435439E4}" name="SeCommandDay" totalsRowFunction="sum" dataDxfId="94" totalsRowDxfId="37"/>
-    <tableColumn id="17" xr3:uid="{4A01EC43-EE14-4A57-8790-63AD1C10441E}" name="SeCommandNight" totalsRowFunction="sum" dataDxfId="93" totalsRowDxfId="36"/>
-    <tableColumn id="18" xr3:uid="{A2239AA3-C2C3-451B-A2A2-60C04EDEE6F8}" name="MeIcusDay" totalsRowFunction="sum" dataDxfId="92" totalsRowDxfId="35"/>
-    <tableColumn id="19" xr3:uid="{ECBDA53E-F388-4471-8A51-D64F6CA99F19}" name="MeIcusNight" totalsRowFunction="sum" dataDxfId="91" totalsRowDxfId="34"/>
-    <tableColumn id="20" xr3:uid="{27DA3BE1-5062-4E05-9011-130B57ABC06D}" name="MeDualDay" totalsRowFunction="sum" dataDxfId="90" totalsRowDxfId="33"/>
-    <tableColumn id="21" xr3:uid="{29820283-7307-4F78-B87D-C36611B4DDD3}" name="MeDualNight" totalsRowFunction="sum" dataDxfId="89" totalsRowDxfId="32"/>
-    <tableColumn id="22" xr3:uid="{152C87A1-34A8-4A96-8523-01A7DF8751C5}" name="MeCommandDay" totalsRowFunction="sum" dataDxfId="88" totalsRowDxfId="31"/>
-    <tableColumn id="23" xr3:uid="{61E0C9F1-CFD0-42E5-A7DC-2C41309F344C}" name="MeCommandNight" totalsRowFunction="sum" dataDxfId="87" totalsRowDxfId="30"/>
-    <tableColumn id="24" xr3:uid="{ADC4E9A8-C2BB-4203-AD5D-C0E8E6DD1FEF}" name="CopilotDay" totalsRowFunction="sum" dataDxfId="86" totalsRowDxfId="29"/>
-    <tableColumn id="25" xr3:uid="{FAA08A34-D45C-4AB5-83C7-9DB2A8B0C2E3}" name="CopilotNight" totalsRowFunction="sum" dataDxfId="85" totalsRowDxfId="28"/>
-    <tableColumn id="26" xr3:uid="{2C960429-5AF1-4AB6-A6DC-6DA0D3E44FE8}" name="IfrIf" totalsRowFunction="sum" dataDxfId="84" totalsRowDxfId="27"/>
-    <tableColumn id="27" xr3:uid="{FADE530A-F0C4-4ADF-96CA-8E4406906F48}" name="IfrSim" totalsRowFunction="sum" dataDxfId="83" totalsRowDxfId="26"/>
-    <tableColumn id="28" xr3:uid="{1ABCF964-1A5D-4D44-94AD-A0AEA9405B55}" name="LandingsDay" totalsRowFunction="sum" dataDxfId="82" totalsRowDxfId="25"/>
-    <tableColumn id="29" xr3:uid="{402C33EC-355B-4E27-9EDC-61E77D1949DA}" name="LandingsNight" totalsRowFunction="sum" dataDxfId="81" totalsRowDxfId="24"/>
-    <tableColumn id="30" xr3:uid="{B49D717E-472F-4145-9125-1A5E9E338FAD}" name="ILS" totalsRowFunction="sum" dataDxfId="80" totalsRowDxfId="23"/>
-    <tableColumn id="31" xr3:uid="{3D63FAA1-0E05-4BEC-9D6B-6D9D19465958}" name="VOR" totalsRowFunction="sum" dataDxfId="79" totalsRowDxfId="22"/>
-    <tableColumn id="32" xr3:uid="{00BE2531-4BA9-460D-B922-80C609F07A18}" name="RNP" totalsRowFunction="sum" dataDxfId="78" totalsRowDxfId="21"/>
-    <tableColumn id="33" xr3:uid="{DCC3F16C-616F-41F1-BA39-755856D47AF1}" name="NDB" totalsRowFunction="sum" dataDxfId="77" totalsRowDxfId="20"/>
-    <tableColumn id="34" xr3:uid="{19FB5B5C-450E-4FCD-B6AD-F55217E6EEFE}" name="DGA (CDI)" totalsRowFunction="sum" dataDxfId="76" totalsRowDxfId="19"/>
-    <tableColumn id="35" xr3:uid="{6D9A8927-28A8-42D9-8C00-39BDAD87B064}" name="DGA (Azi)" totalsRowFunction="sum" dataDxfId="75" totalsRowDxfId="18"/>
-    <tableColumn id="36" xr3:uid="{F52CFC91-2462-4865-A135-E24F1A59D2F9}" name="Circling" totalsRowFunction="sum" dataDxfId="74" totalsRowDxfId="17"/>
-    <tableColumn id="54" xr3:uid="{FA8413FA-CA54-4EB0-A142-59A7B4A9BE3A}" name="TotalHours" totalsRowFunction="sum" dataDxfId="73" totalsRowDxfId="16">
+    <tableColumn id="62" xr3:uid="{35D88777-AA03-4EF0-B227-9E2048B1AA5E}" name="Details" dataDxfId="93" totalsRowDxfId="92"/>
+    <tableColumn id="9" xr3:uid="{C53B3FE9-B5B3-4FE4-9D2F-CC5CB5F157FB}" name="Custom 1" totalsRowFunction="sum" dataDxfId="91" totalsRowDxfId="90"/>
+    <tableColumn id="10" xr3:uid="{D4DF1EA3-5D43-434F-AEBE-A605D9FFD457}" name="Custom 2" totalsRowFunction="sum" dataDxfId="89" totalsRowDxfId="88"/>
+    <tableColumn id="11" xr3:uid="{741C7510-6E1A-49A3-9C9E-E42097510CEC}" name="Custom 3" totalsRowFunction="sum" dataDxfId="87" totalsRowDxfId="86"/>
+    <tableColumn id="57" xr3:uid="{4E4B2A2B-F980-49E5-9F31-D9E96FB9A587}" name="Custom 4" totalsRowFunction="sum" dataDxfId="85" totalsRowDxfId="84"/>
+    <tableColumn id="12" xr3:uid="{EC4A1A18-0A2D-49AC-BFCD-E01030F64888}" name="SeIcusDay" totalsRowFunction="sum" dataDxfId="83" totalsRowDxfId="82"/>
+    <tableColumn id="13" xr3:uid="{40EA09A9-61CC-4653-B74B-0553995DCA63}" name="SeIcusNight" totalsRowFunction="sum" dataDxfId="81" totalsRowDxfId="80"/>
+    <tableColumn id="14" xr3:uid="{482A4ED7-9580-4817-A603-06ECE9BF848E}" name="SeDualDay" totalsRowFunction="sum" dataDxfId="79" totalsRowDxfId="78"/>
+    <tableColumn id="15" xr3:uid="{ECD3AC03-3033-4736-ACF4-108BA4CADCA9}" name="SeDualNight" totalsRowFunction="sum" dataDxfId="77" totalsRowDxfId="76"/>
+    <tableColumn id="16" xr3:uid="{0D5B8F94-E65D-4CF8-BCFB-AB7B435439E4}" name="SeCommandDay" totalsRowFunction="sum" dataDxfId="75" totalsRowDxfId="74"/>
+    <tableColumn id="17" xr3:uid="{4A01EC43-EE14-4A57-8790-63AD1C10441E}" name="SeCommandNight" totalsRowFunction="sum" dataDxfId="73" totalsRowDxfId="72"/>
+    <tableColumn id="18" xr3:uid="{A2239AA3-C2C3-451B-A2A2-60C04EDEE6F8}" name="MeIcusDay" totalsRowFunction="sum" dataDxfId="71" totalsRowDxfId="70"/>
+    <tableColumn id="19" xr3:uid="{ECBDA53E-F388-4471-8A51-D64F6CA99F19}" name="MeIcusNight" totalsRowFunction="sum" dataDxfId="69" totalsRowDxfId="68"/>
+    <tableColumn id="20" xr3:uid="{27DA3BE1-5062-4E05-9011-130B57ABC06D}" name="MeDualDay" totalsRowFunction="sum" dataDxfId="67" totalsRowDxfId="66"/>
+    <tableColumn id="21" xr3:uid="{29820283-7307-4F78-B87D-C36611B4DDD3}" name="MeDualNight" totalsRowFunction="sum" dataDxfId="65" totalsRowDxfId="64"/>
+    <tableColumn id="22" xr3:uid="{152C87A1-34A8-4A96-8523-01A7DF8751C5}" name="MeCommandDay" totalsRowFunction="sum" dataDxfId="63" totalsRowDxfId="62"/>
+    <tableColumn id="23" xr3:uid="{61E0C9F1-CFD0-42E5-A7DC-2C41309F344C}" name="MeCommandNight" totalsRowFunction="sum" dataDxfId="61" totalsRowDxfId="60"/>
+    <tableColumn id="24" xr3:uid="{ADC4E9A8-C2BB-4203-AD5D-C0E8E6DD1FEF}" name="CopilotDay" totalsRowFunction="sum" dataDxfId="59" totalsRowDxfId="58"/>
+    <tableColumn id="25" xr3:uid="{FAA08A34-D45C-4AB5-83C7-9DB2A8B0C2E3}" name="CopilotNight" totalsRowFunction="sum" dataDxfId="57" totalsRowDxfId="56"/>
+    <tableColumn id="26" xr3:uid="{2C960429-5AF1-4AB6-A6DC-6DA0D3E44FE8}" name="IfrIf" totalsRowFunction="sum" dataDxfId="55" totalsRowDxfId="54"/>
+    <tableColumn id="27" xr3:uid="{FADE530A-F0C4-4ADF-96CA-8E4406906F48}" name="IfrSim" totalsRowFunction="sum" dataDxfId="53" totalsRowDxfId="52"/>
+    <tableColumn id="28" xr3:uid="{1ABCF964-1A5D-4D44-94AD-A0AEA9405B55}" name="LandingsDay" totalsRowFunction="sum" dataDxfId="51" totalsRowDxfId="50"/>
+    <tableColumn id="29" xr3:uid="{402C33EC-355B-4E27-9EDC-61E77D1949DA}" name="LandingsNight" totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="48"/>
+    <tableColumn id="30" xr3:uid="{B49D717E-472F-4145-9125-1A5E9E338FAD}" name="ILS" totalsRowFunction="sum" dataDxfId="47" totalsRowDxfId="46"/>
+    <tableColumn id="31" xr3:uid="{3D63FAA1-0E05-4BEC-9D6B-6D9D19465958}" name="VOR" totalsRowFunction="sum" dataDxfId="45" totalsRowDxfId="44"/>
+    <tableColumn id="32" xr3:uid="{00BE2531-4BA9-460D-B922-80C609F07A18}" name="RNP" totalsRowFunction="sum" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="33" xr3:uid="{DCC3F16C-616F-41F1-BA39-755856D47AF1}" name="NDB" totalsRowFunction="sum" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="34" xr3:uid="{19FB5B5C-450E-4FCD-B6AD-F55217E6EEFE}" name="DGA (CDI)" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="35" xr3:uid="{6D9A8927-28A8-42D9-8C00-39BDAD87B064}" name="DGA (Azi)" totalsRowFunction="sum" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="36" xr3:uid="{F52CFC91-2462-4865-A135-E24F1A59D2F9}" name="Circling" totalsRowFunction="sum" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="54" xr3:uid="{FA8413FA-CA54-4EB0-A142-59A7B4A9BE3A}" name="TotalHours" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="32">
       <calculatedColumnFormula>SUM(Logbook[[#This Row],[SeIcusDay]:[CopilotNight]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{6F315B7F-6161-4654-A259-C403C03FD38C}" name="TotalApps" totalsRowFunction="sum" dataDxfId="72" totalsRowDxfId="15">
+    <tableColumn id="37" xr3:uid="{6F315B7F-6161-4654-A259-C403C03FD38C}" name="TotalApps" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
       <calculatedColumnFormula>SUM(Logbook[[#This Row],[ILS]:[DGA (Azi)]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{FC445918-ECBA-41EC-A2CD-AAD3627DAC1A}" name="CumLandingsDay" dataDxfId="71" totalsRowDxfId="14">
+    <tableColumn id="39" xr3:uid="{FC445918-ECBA-41EC-A2CD-AAD3627DAC1A}" name="CumLandingsDay" dataDxfId="29" totalsRowDxfId="28">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumLandingsDay]),Logbook[[#This Row],[LandingsDay]],Logbook[[#This Row],[LandingsDay]]+INDEX(Logbook[CumLandingsDay],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{7EDEE77D-C37A-462D-A6BA-2FE217273635}" name="CumLandingsNight" dataDxfId="70" totalsRowDxfId="13">
+    <tableColumn id="40" xr3:uid="{7EDEE77D-C37A-462D-A6BA-2FE217273635}" name="CumLandingsNight" dataDxfId="27" totalsRowDxfId="26">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumLandingsNight]),Logbook[[#This Row],[LandingsNight]],Logbook[[#This Row],[LandingsNight]]+INDEX(Logbook[CumLandingsNight],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{26B7EE4D-23EF-49CC-B3B7-76C866CA9AB5}" name="CumILS" dataDxfId="69" totalsRowDxfId="12">
+    <tableColumn id="41" xr3:uid="{26B7EE4D-23EF-49CC-B3B7-76C866CA9AB5}" name="CumILS" dataDxfId="25" totalsRowDxfId="24">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumILS]),Logbook[[#This Row],[ILS]],Logbook[[#This Row],[ILS]]+INDEX(Logbook[CumILS],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{535B9677-818A-48BF-95F1-87A2ED8DAC0E}" name="CumVOR" dataDxfId="68" totalsRowDxfId="11">
+    <tableColumn id="42" xr3:uid="{535B9677-818A-48BF-95F1-87A2ED8DAC0E}" name="CumVOR" dataDxfId="23" totalsRowDxfId="22">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumVOR]),Logbook[[#This Row],[VOR]],Logbook[[#This Row],[VOR]]+INDEX(Logbook[CumVOR],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="43" xr3:uid="{144757E6-C50D-4123-B1DB-42C7FF7BA87A}" name="CumRNP" dataDxfId="67" totalsRowDxfId="10">
+    <tableColumn id="43" xr3:uid="{144757E6-C50D-4123-B1DB-42C7FF7BA87A}" name="CumRNP" dataDxfId="21" totalsRowDxfId="20">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumRNP]),Logbook[[#This Row],[RNP]],Logbook[[#This Row],[RNP]]+INDEX(Logbook[CumRNP],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{73B414DB-72DC-4DDF-86A1-A0219BB39101}" name="CumNDB" dataDxfId="66" totalsRowDxfId="9">
+    <tableColumn id="44" xr3:uid="{73B414DB-72DC-4DDF-86A1-A0219BB39101}" name="CumNDB" dataDxfId="19" totalsRowDxfId="18">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumNDB]),Logbook[[#This Row],[NDB]],Logbook[[#This Row],[NDB]]+INDEX(Logbook[CumNDB],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{AFA0920F-834E-4312-94D5-1BB65D1BD529}" name="CumDgaCdi" dataDxfId="65" totalsRowDxfId="8">
+    <tableColumn id="45" xr3:uid="{AFA0920F-834E-4312-94D5-1BB65D1BD529}" name="CumDgaCdi" dataDxfId="17" totalsRowDxfId="16">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumDgaCdi]),Logbook[[#This Row],[DGA (CDI)]],Logbook[[#This Row],[DGA (CDI)]]+INDEX(Logbook[CumDgaCdi],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="46" xr3:uid="{DE0A8510-855B-4C7A-9DC5-4006EA854638}" name="CumDgaAzi" dataDxfId="64" totalsRowDxfId="7">
+    <tableColumn id="46" xr3:uid="{DE0A8510-855B-4C7A-9DC5-4006EA854638}" name="CumDgaAzi" dataDxfId="15" totalsRowDxfId="14">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumDgaAzi]),Logbook[[#This Row],[DGA (Azi)]],Logbook[[#This Row],[DGA (Azi)]]+INDEX(Logbook[CumDgaAzi],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="47" xr3:uid="{2E62ECFC-8938-43ED-A7A3-96021161E246}" name="CumCirc" dataDxfId="63" totalsRowDxfId="6">
+    <tableColumn id="47" xr3:uid="{2E62ECFC-8938-43ED-A7A3-96021161E246}" name="CumCirc" dataDxfId="13" totalsRowDxfId="12">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumCirc]),Logbook[[#This Row],[Circling]],Logbook[[#This Row],[Circling]]+INDEX(Logbook[CumCirc],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="48" xr3:uid="{27CD4B83-2190-43DC-845B-C2367A3B9709}" name="CumTotalApps" dataDxfId="62" totalsRowDxfId="5">
+    <tableColumn id="48" xr3:uid="{27CD4B83-2190-43DC-845B-C2367A3B9709}" name="CumTotalApps" dataDxfId="11" totalsRowDxfId="10">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumTotalApps]),Logbook[[#This Row],[TotalApps]],Logbook[[#This Row],[TotalApps]]+INDEX(Logbook[CumTotalApps],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="49" xr3:uid="{194F9066-B2DA-4EC2-9D85-921E960CF0B3}" name="CumTotalHours" dataDxfId="61" totalsRowDxfId="4">
+    <tableColumn id="49" xr3:uid="{194F9066-B2DA-4EC2-9D85-921E960CF0B3}" name="CumTotalHours" dataDxfId="9" totalsRowDxfId="8">
       <calculatedColumnFormula>SUM(INDEX(Logbook[TotalHours],1):Logbook[[#This Row],[TotalHours]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="50" xr3:uid="{D904A10A-DC61-4EF5-A0A7-8E4E66C716B2}" name="Cum2D" dataDxfId="60" totalsRowDxfId="3">
+    <tableColumn id="50" xr3:uid="{D904A10A-DC61-4EF5-A0A7-8E4E66C716B2}" name="Cum2D" dataDxfId="7" totalsRowDxfId="6">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[Cum2D]),SUM(Logbook[[#This Row],[VOR]:[DGA (Azi)]]),SUM(Logbook[[#This Row],[VOR]:[DGA (Azi)]])+INDEX(Logbook[Cum2D],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="51" xr3:uid="{53B0F290-2D6B-4939-856F-DDDAEF901884}" name="Cum3D" dataDxfId="59" totalsRowDxfId="2">
+    <tableColumn id="51" xr3:uid="{53B0F290-2D6B-4939-856F-DDDAEF901884}" name="Cum3D" dataDxfId="5" totalsRowDxfId="4">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[Cum3D]),Logbook[[#This Row],[ILS]],Logbook[[#This Row],[ILS]]+INDEX(Logbook[Cum3D],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="52" xr3:uid="{2B647697-03EA-4F4D-93DD-5D0A77657840}" name="CumCDI" dataDxfId="58" totalsRowDxfId="1">
+    <tableColumn id="52" xr3:uid="{2B647697-03EA-4F4D-93DD-5D0A77657840}" name="CumCDI" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumCDI]),SUM(Logbook[[#This Row],[ILS]:[RNP]])+Logbook[[#This Row],[DGA (CDI)]],SUM(Logbook[[#This Row],[ILS]:[RNP]])+Logbook[[#This Row],[DGA (CDI)]]+INDEX(Logbook[CumCDI],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="55" xr3:uid="{18C8F4D1-667B-429B-9365-8A96E578D433}" name="CumAzi" dataDxfId="57" totalsRowDxfId="0">
+    <tableColumn id="55" xr3:uid="{18C8F4D1-667B-429B-9365-8A96E578D433}" name="CumAzi" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumAzi]),Logbook[[#This Row],[NDB]]+Logbook[[#This Row],[DGA (Azi)]],Logbook[[#This Row],[NDB]]+Logbook[[#This Row],[DGA (Azi)]]+INDEX(Logbook[CumAzi],ROW()-ROW(Logbook[#Headers])+1))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5672,51 +5699,51 @@
   <dimension ref="A1:BV104"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" style="36" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" style="36" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="37" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="38" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" style="39" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" style="40" customWidth="1"/>
-    <col min="7" max="8" width="9.7109375" style="36" customWidth="1"/>
-    <col min="9" max="9" width="13" style="36" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19" style="36" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" style="36" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.7109375" style="36" customWidth="1"/>
-    <col min="13" max="14" width="14.28515625" style="41" customWidth="1"/>
-    <col min="15" max="16" width="14.28515625" style="38" customWidth="1"/>
-    <col min="17" max="34" width="6.28515625" style="36" customWidth="1"/>
-    <col min="35" max="41" width="7.7109375" style="36" customWidth="1"/>
-    <col min="42" max="42" width="15.28515625" style="41" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="14.42578125" style="42" hidden="1" customWidth="1"/>
-    <col min="44" max="44" width="16.28515625" style="36" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="17.7109375" style="36" hidden="1" customWidth="1"/>
-    <col min="46" max="46" width="7.42578125" style="36" hidden="1" customWidth="1"/>
-    <col min="47" max="47" width="8.7109375" style="36" hidden="1" customWidth="1"/>
-    <col min="48" max="48" width="10.28515625" style="36" hidden="1" customWidth="1"/>
-    <col min="49" max="49" width="8.7109375" style="36" hidden="1" customWidth="1"/>
-    <col min="50" max="50" width="11.28515625" style="36" hidden="1" customWidth="1"/>
-    <col min="51" max="51" width="11" style="36" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="8.28515625" style="36" hidden="1" customWidth="1"/>
-    <col min="53" max="53" width="14" style="36" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="14.7109375" style="36" hidden="1" customWidth="1"/>
-    <col min="55" max="56" width="7.42578125" style="36" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="8" style="38" hidden="1" customWidth="1"/>
-    <col min="58" max="58" width="8.42578125" style="36" hidden="1" customWidth="1"/>
-    <col min="59" max="59" width="3.7109375" style="36" customWidth="1"/>
-    <col min="60" max="60" width="0" style="36" hidden="1" customWidth="1"/>
-    <col min="61" max="61" width="8" style="36" hidden="1" customWidth="1"/>
-    <col min="62" max="62" width="8.42578125" style="36" hidden="1" customWidth="1"/>
-    <col min="63" max="64" width="0" style="36" hidden="1" customWidth="1"/>
-    <col min="65" max="65" width="8.42578125" style="36" hidden="1" customWidth="1"/>
-    <col min="66" max="68" width="0" style="36" hidden="1" customWidth="1"/>
-    <col min="69" max="70" width="0" style="36" hidden="1"/>
-    <col min="71" max="71" width="8.42578125" style="36" hidden="1"/>
-    <col min="72" max="74" width="0" style="36" hidden="1"/>
-    <col min="75" max="16384" width="9.28515625" style="36" hidden="1"/>
+    <col min="1" max="1" width="3.7109375" style="30" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" style="30" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="31" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" style="32" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" style="33" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" style="34" customWidth="1"/>
+    <col min="7" max="8" width="9.7109375" style="30" customWidth="1"/>
+    <col min="9" max="9" width="13" style="30" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" style="30" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.7109375" style="30" customWidth="1"/>
+    <col min="13" max="14" width="14.28515625" style="35" customWidth="1"/>
+    <col min="15" max="16" width="14.28515625" style="32" customWidth="1"/>
+    <col min="17" max="34" width="6.28515625" style="30" customWidth="1"/>
+    <col min="35" max="41" width="7.7109375" style="30" customWidth="1"/>
+    <col min="42" max="42" width="15.28515625" style="35" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="14.42578125" style="36" hidden="1" customWidth="1"/>
+    <col min="44" max="44" width="16.28515625" style="30" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="17.7109375" style="30" hidden="1" customWidth="1"/>
+    <col min="46" max="46" width="7.42578125" style="30" hidden="1" customWidth="1"/>
+    <col min="47" max="47" width="8.7109375" style="30" hidden="1" customWidth="1"/>
+    <col min="48" max="48" width="10.28515625" style="30" hidden="1" customWidth="1"/>
+    <col min="49" max="49" width="8.7109375" style="30" hidden="1" customWidth="1"/>
+    <col min="50" max="50" width="11.28515625" style="30" hidden="1" customWidth="1"/>
+    <col min="51" max="51" width="11" style="30" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="8.28515625" style="30" hidden="1" customWidth="1"/>
+    <col min="53" max="53" width="14" style="30" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="14.7109375" style="30" hidden="1" customWidth="1"/>
+    <col min="55" max="56" width="7.42578125" style="30" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="8" style="32" hidden="1" customWidth="1"/>
+    <col min="58" max="58" width="8.42578125" style="30" hidden="1" customWidth="1"/>
+    <col min="59" max="59" width="3.7109375" style="30" customWidth="1"/>
+    <col min="60" max="60" width="0" style="30" hidden="1" customWidth="1"/>
+    <col min="61" max="61" width="8" style="30" hidden="1" customWidth="1"/>
+    <col min="62" max="62" width="8.42578125" style="30" hidden="1" customWidth="1"/>
+    <col min="63" max="64" width="0" style="30" hidden="1" customWidth="1"/>
+    <col min="65" max="65" width="8.42578125" style="30" hidden="1" customWidth="1"/>
+    <col min="66" max="68" width="0" style="30" hidden="1" customWidth="1"/>
+    <col min="69" max="70" width="0" style="30" hidden="1"/>
+    <col min="71" max="71" width="8.42578125" style="30" hidden="1"/>
+    <col min="72" max="74" width="0" style="30" hidden="1"/>
+    <col min="75" max="16384" width="9.28515625" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A1"/>
       <c r="BM1"/>
       <c r="BN1"/>
@@ -5729,92 +5756,92 @@
       <c r="BU1"/>
       <c r="BV1"/>
     </row>
-    <row r="2" spans="1:74" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:74" s="37" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="101" t="s">
+      <c r="B2" s="30"/>
+      <c r="C2" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="92" t="s">
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="96"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="92" t="s">
+      <c r="H2" s="76"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="93"/>
-      <c r="L2" s="96" t="s">
+      <c r="K2" s="73"/>
+      <c r="L2" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="M2" s="92" t="s">
+      <c r="M2" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="93"/>
-      <c r="Q2" s="78" t="s">
+      <c r="N2" s="76"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="78"/>
-      <c r="U2" s="78"/>
-      <c r="V2" s="78"/>
-      <c r="W2" s="78" t="s">
+      <c r="R2" s="58"/>
+      <c r="S2" s="58"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="58"/>
+      <c r="V2" s="58"/>
+      <c r="W2" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="X2" s="78"/>
-      <c r="Y2" s="78"/>
-      <c r="Z2" s="78"/>
-      <c r="AA2" s="78"/>
-      <c r="AB2" s="78"/>
-      <c r="AC2" s="92" t="s">
+      <c r="X2" s="58"/>
+      <c r="Y2" s="58"/>
+      <c r="Z2" s="58"/>
+      <c r="AA2" s="58"/>
+      <c r="AB2" s="58"/>
+      <c r="AC2" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="AD2" s="93"/>
-      <c r="AE2" s="78" t="s">
+      <c r="AD2" s="73"/>
+      <c r="AE2" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="AF2" s="78"/>
-      <c r="AG2" s="88" t="s">
+      <c r="AF2" s="58"/>
+      <c r="AG2" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="AH2" s="89"/>
-      <c r="AI2" s="78" t="s">
+      <c r="AH2" s="69"/>
+      <c r="AI2" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="AJ2" s="78"/>
-      <c r="AK2" s="78"/>
-      <c r="AL2" s="78"/>
-      <c r="AM2" s="78"/>
-      <c r="AN2" s="78"/>
-      <c r="AO2" s="86"/>
-      <c r="AP2" s="80" t="s">
+      <c r="AJ2" s="58"/>
+      <c r="AK2" s="58"/>
+      <c r="AL2" s="58"/>
+      <c r="AM2" s="58"/>
+      <c r="AN2" s="58"/>
+      <c r="AO2" s="66"/>
+      <c r="AP2" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="AQ2" s="81"/>
-      <c r="AR2" s="110" t="s">
+      <c r="AQ2" s="61"/>
+      <c r="AR2" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="AS2" s="111"/>
-      <c r="AT2" s="111"/>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
-      <c r="AW2" s="111"/>
-      <c r="AX2" s="111"/>
-      <c r="AY2" s="111"/>
-      <c r="AZ2" s="111"/>
-      <c r="BA2" s="111"/>
-      <c r="BB2" s="111"/>
-      <c r="BC2" s="111"/>
-      <c r="BD2" s="111"/>
-      <c r="BE2" s="111"/>
-      <c r="BF2" s="112"/>
-      <c r="BG2" s="36"/>
+      <c r="AS2" s="91"/>
+      <c r="AT2" s="91"/>
+      <c r="AU2" s="91"/>
+      <c r="AV2" s="91"/>
+      <c r="AW2" s="91"/>
+      <c r="AX2" s="91"/>
+      <c r="AY2" s="91"/>
+      <c r="AZ2" s="91"/>
+      <c r="BA2" s="91"/>
+      <c r="BB2" s="91"/>
+      <c r="BC2" s="91"/>
+      <c r="BD2" s="91"/>
+      <c r="BE2" s="91"/>
+      <c r="BF2" s="92"/>
+      <c r="BG2" s="30"/>
       <c r="BM2"/>
       <c r="BN2"/>
       <c r="BO2"/>
@@ -5826,114 +5853,114 @@
       <c r="BU2"/>
       <c r="BV2"/>
     </row>
-    <row r="3" spans="1:74" s="43" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:74" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="97"/>
-      <c r="N3" s="98"/>
-      <c r="O3" s="98"/>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="79" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="78"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79" t="s">
+      <c r="R3" s="59"/>
+      <c r="S3" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="79"/>
-      <c r="U3" s="79" t="s">
+      <c r="T3" s="59"/>
+      <c r="U3" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="V3" s="79"/>
-      <c r="W3" s="79" t="s">
+      <c r="V3" s="59"/>
+      <c r="W3" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="79" t="s">
+      <c r="X3" s="59"/>
+      <c r="Y3" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79" t="s">
+      <c r="Z3" s="59"/>
+      <c r="AA3" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="AB3" s="79"/>
-      <c r="AC3" s="94"/>
-      <c r="AD3" s="95"/>
-      <c r="AE3" s="79" t="s">
+      <c r="AB3" s="59"/>
+      <c r="AC3" s="74"/>
+      <c r="AD3" s="75"/>
+      <c r="AE3" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="AF3" s="79" t="s">
+      <c r="AF3" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="AG3" s="90" t="s">
+      <c r="AG3" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="AH3" s="90" t="s">
+      <c r="AH3" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="AI3" s="79" t="s">
+      <c r="AI3" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="AJ3" s="79" t="s">
+      <c r="AJ3" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="AK3" s="79" t="s">
+      <c r="AK3" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="AL3" s="79" t="s">
+      <c r="AL3" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="AM3" s="79" t="s">
+      <c r="AM3" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="AN3" s="79" t="s">
+      <c r="AN3" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="AO3" s="87" t="s">
+      <c r="AO3" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="AP3" s="82"/>
-      <c r="AQ3" s="83"/>
-      <c r="AR3" s="110" t="s">
+      <c r="AP3" s="62"/>
+      <c r="AQ3" s="63"/>
+      <c r="AR3" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="AS3" s="112"/>
-      <c r="AT3" s="110" t="s">
+      <c r="AS3" s="92"/>
+      <c r="AT3" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="AU3" s="111"/>
-      <c r="AV3" s="111"/>
-      <c r="AW3" s="111"/>
-      <c r="AX3" s="111"/>
-      <c r="AY3" s="111"/>
-      <c r="AZ3" s="112"/>
-      <c r="BA3" s="113" t="s">
+      <c r="AU3" s="91"/>
+      <c r="AV3" s="91"/>
+      <c r="AW3" s="91"/>
+      <c r="AX3" s="91"/>
+      <c r="AY3" s="91"/>
+      <c r="AZ3" s="92"/>
+      <c r="BA3" s="93" t="s">
         <v>61</v>
       </c>
-      <c r="BB3" s="114"/>
-      <c r="BC3" s="115" t="s">
+      <c r="BB3" s="94"/>
+      <c r="BC3" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="BD3" s="115" t="s">
+      <c r="BD3" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="BE3" s="115" t="s">
+      <c r="BE3" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="BF3" s="109" t="s">
+      <c r="BF3" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="BG3" s="36"/>
+      <c r="BG3" s="30"/>
       <c r="BM3"/>
       <c r="BN3"/>
       <c r="BO3"/>
@@ -5945,116 +5972,116 @@
       <c r="BU3"/>
       <c r="BV3"/>
     </row>
-    <row r="4" spans="1:74" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:74" s="37" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="46" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="107" t="s">
+      <c r="D4" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="107"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="95"/>
-      <c r="L4" s="100"/>
-      <c r="M4" s="94"/>
-      <c r="N4" s="100"/>
-      <c r="O4" s="100"/>
-      <c r="P4" s="95"/>
-      <c r="Q4" s="44" t="s">
+      <c r="E4" s="87"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="R4" s="44" t="s">
+      <c r="R4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="S4" s="44" t="s">
+      <c r="S4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="T4" s="44" t="s">
+      <c r="T4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="U4" s="44" t="s">
+      <c r="U4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="V4" s="44" t="s">
+      <c r="V4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="W4" s="44" t="s">
+      <c r="W4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="X4" s="44" t="s">
+      <c r="X4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="Y4" s="44" t="s">
+      <c r="Y4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="Z4" s="44" t="s">
+      <c r="Z4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AA4" s="44" t="s">
+      <c r="AA4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="AB4" s="44" t="s">
+      <c r="AB4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AC4" s="44" t="s">
+      <c r="AC4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="AD4" s="44" t="s">
+      <c r="AD4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AE4" s="79"/>
-      <c r="AF4" s="79"/>
-      <c r="AG4" s="91"/>
-      <c r="AH4" s="91"/>
-      <c r="AI4" s="79"/>
-      <c r="AJ4" s="79"/>
-      <c r="AK4" s="79"/>
-      <c r="AL4" s="79"/>
-      <c r="AM4" s="79"/>
-      <c r="AN4" s="79"/>
-      <c r="AO4" s="87"/>
-      <c r="AP4" s="84"/>
-      <c r="AQ4" s="85"/>
-      <c r="AR4" s="45" t="s">
+      <c r="AE4" s="59"/>
+      <c r="AF4" s="59"/>
+      <c r="AG4" s="71"/>
+      <c r="AH4" s="71"/>
+      <c r="AI4" s="59"/>
+      <c r="AJ4" s="59"/>
+      <c r="AK4" s="59"/>
+      <c r="AL4" s="59"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="59"/>
+      <c r="AO4" s="67"/>
+      <c r="AP4" s="64"/>
+      <c r="AQ4" s="65"/>
+      <c r="AR4" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="AS4" s="45" t="s">
+      <c r="AS4" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="AT4" s="45" t="s">
+      <c r="AT4" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AU4" s="45" t="s">
+      <c r="AU4" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="AV4" s="45" t="s">
+      <c r="AV4" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="AW4" s="45" t="s">
+      <c r="AW4" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="AX4" s="45" t="s">
+      <c r="AX4" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="AY4" s="45" t="s">
+      <c r="AY4" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="AZ4" s="45" t="s">
+      <c r="AZ4" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="BA4" s="94"/>
-      <c r="BB4" s="95"/>
-      <c r="BC4" s="115"/>
-      <c r="BD4" s="115"/>
-      <c r="BE4" s="115"/>
-      <c r="BF4" s="109"/>
-      <c r="BG4" s="36"/>
+      <c r="BA4" s="74"/>
+      <c r="BB4" s="75"/>
+      <c r="BC4" s="95"/>
+      <c r="BD4" s="95"/>
+      <c r="BE4" s="95"/>
+      <c r="BF4" s="89"/>
+      <c r="BG4" s="30"/>
       <c r="BM4"/>
       <c r="BN4"/>
       <c r="BO4"/>
@@ -6066,180 +6093,180 @@
       <c r="BU4"/>
       <c r="BV4"/>
     </row>
-    <row r="5" spans="1:74" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:74" s="37" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="N5" s="12" t="s">
+      <c r="N5" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="O5" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="P5" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="Q5" s="23" t="s">
+      <c r="Q5" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="R5" s="23" t="s">
+      <c r="R5" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="S5" s="23" t="s">
+      <c r="S5" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="T5" s="23" t="s">
+      <c r="T5" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="U5" s="23" t="s">
+      <c r="U5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="V5" s="23" t="s">
+      <c r="V5" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="W5" s="23" t="s">
+      <c r="W5" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="X5" s="23" t="s">
+      <c r="X5" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="Y5" s="23" t="s">
+      <c r="Y5" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Z5" s="23" t="s">
+      <c r="Z5" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="AA5" s="23" t="s">
+      <c r="AA5" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="AB5" s="23" t="s">
+      <c r="AB5" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="AC5" s="23" t="s">
+      <c r="AC5" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="AD5" s="23" t="s">
+      <c r="AD5" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="AE5" s="23" t="s">
+      <c r="AE5" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="AF5" s="23" t="s">
+      <c r="AF5" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="AG5" s="24" t="s">
+      <c r="AG5" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="AH5" s="25" t="s">
+      <c r="AH5" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="AI5" s="30" t="s">
+      <c r="AI5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="AJ5" s="25" t="s">
+      <c r="AJ5" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="AK5" s="30" t="s">
+      <c r="AK5" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="AL5" s="25" t="s">
+      <c r="AL5" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="AM5" s="30" t="s">
+      <c r="AM5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="AN5" s="25" t="s">
+      <c r="AN5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="AO5" s="26" t="s">
+      <c r="AO5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="AP5" s="14" t="s">
+      <c r="AP5" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="AQ5" s="15" t="s">
+      <c r="AQ5" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AR5" s="16" t="s">
+      <c r="AR5" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="AS5" s="16" t="s">
+      <c r="AS5" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AT5" s="16" t="s">
+      <c r="AT5" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AU5" s="16" t="s">
+      <c r="AU5" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AV5" s="16" t="s">
+      <c r="AV5" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="AW5" s="16" t="s">
+      <c r="AW5" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="AX5" s="16" t="s">
+      <c r="AX5" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="AY5" s="16" t="s">
+      <c r="AY5" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="AZ5" s="16" t="s">
+      <c r="AZ5" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="BA5" s="17" t="s">
+      <c r="BA5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="BB5" s="18" t="s">
+      <c r="BB5" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="BC5" s="19" t="s">
+      <c r="BC5" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="BD5" s="18" t="s">
+      <c r="BD5" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="BE5" s="18" t="s">
+      <c r="BE5" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="BF5" s="20" t="s">
+      <c r="BF5" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="BG5" s="36"/>
+      <c r="BG5" s="30"/>
       <c r="BM5"/>
       <c r="BN5"/>
       <c r="BO5"/>
@@ -6251,120 +6278,120 @@
       <c r="BU5"/>
       <c r="BV5"/>
     </row>
-    <row r="6" spans="1:74" s="22" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:74" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="47" t="e">
+      <c r="B6" s="96"/>
+      <c r="C6" s="97" t="e">
         <f>IFERROR(IF(DAY(DATE(Logbook[[#This Row],[Year]],IF(ISNUMBER(Logbook[[#This Row],[Month]]),MONTH(Logbook[[#This Row],[Month]]),MONTH(DATEVALUE(Logbook[[#This Row],[Month]]&amp;" 1"))),IF(ISNUMBER(Logbook[[#This Row],[Day]]),IF(Logbook[[#This Row],[Day]]&gt;31,DAY(Logbook[[#This Row],[Day]]),Logbook[[#This Row],[Day]]),VALUE(Logbook[[#This Row],[Day]]))))&lt;&gt;IF(ISNUMBER(Logbook[[#This Row],[Day]]),IF(Logbook[[#This Row],[Day]]&gt;31,DAY(Logbook[[#This Row],[Day]]),Logbook[[#This Row],[Day]]),VALUE(Logbook[[#This Row],[Day]])),NA(),DATE(Logbook[[#This Row],[Year]],IF(ISNUMBER(Logbook[[#This Row],[Month]]),MONTH(Logbook[[#This Row],[Month]]),MONTH(DATEVALUE(Logbook[[#This Row],[Month]]&amp;" 1"))),IF(ISNUMBER(Logbook[[#This Row],[Day]]),IF(Logbook[[#This Row],[Day]]&gt;31,DAY(Logbook[[#This Row],[Day]]),Logbook[[#This Row],[Day]]),VALUE(Logbook[[#This Row],[Day]])))),NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
-      <c r="S6" s="33"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="33"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33"/>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="33"/>
-      <c r="AE6" s="33"/>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="32"/>
-      <c r="AH6" s="32"/>
-      <c r="AI6" s="32"/>
-      <c r="AJ6" s="32"/>
-      <c r="AK6" s="32"/>
-      <c r="AL6" s="32"/>
-      <c r="AM6" s="32"/>
-      <c r="AN6" s="32"/>
-      <c r="AO6" s="35"/>
-      <c r="AP6" s="29">
+      <c r="D6" s="24"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="24"/>
+      <c r="AH6" s="24"/>
+      <c r="AI6" s="24"/>
+      <c r="AJ6" s="24"/>
+      <c r="AK6" s="24"/>
+      <c r="AL6" s="24"/>
+      <c r="AM6" s="24"/>
+      <c r="AN6" s="24"/>
+      <c r="AO6" s="27"/>
+      <c r="AP6" s="21">
         <f>SUM(Logbook[[#This Row],[SeIcusDay]:[CopilotNight]])</f>
         <v>0</v>
       </c>
-      <c r="AQ6" s="4">
+      <c r="AQ6" s="100">
         <f>SUM(Logbook[[#This Row],[ILS]:[DGA (Azi)]])</f>
         <v>0</v>
       </c>
-      <c r="AR6" s="27">
+      <c r="AR6" s="101">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumLandingsDay]),Logbook[[#This Row],[LandingsDay]],Logbook[[#This Row],[LandingsDay]]+INDEX(Logbook[CumLandingsDay],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="AS6" s="27">
+      <c r="AS6" s="101">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumLandingsNight]),Logbook[[#This Row],[LandingsNight]],Logbook[[#This Row],[LandingsNight]]+INDEX(Logbook[CumLandingsNight],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="AT6" s="27">
+      <c r="AT6" s="101">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumILS]),Logbook[[#This Row],[ILS]],Logbook[[#This Row],[ILS]]+INDEX(Logbook[CumILS],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="AU6" s="27">
+      <c r="AU6" s="101">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumVOR]),Logbook[[#This Row],[VOR]],Logbook[[#This Row],[VOR]]+INDEX(Logbook[CumVOR],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="AV6" s="27">
+      <c r="AV6" s="101">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumRNP]),Logbook[[#This Row],[RNP]],Logbook[[#This Row],[RNP]]+INDEX(Logbook[CumRNP],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="AW6" s="27">
+      <c r="AW6" s="101">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumNDB]),Logbook[[#This Row],[NDB]],Logbook[[#This Row],[NDB]]+INDEX(Logbook[CumNDB],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="AX6" s="27">
+      <c r="AX6" s="101">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumDgaCdi]),Logbook[[#This Row],[DGA (CDI)]],Logbook[[#This Row],[DGA (CDI)]]+INDEX(Logbook[CumDgaCdi],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="AY6" s="27">
+      <c r="AY6" s="101">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumDgaAzi]),Logbook[[#This Row],[DGA (Azi)]],Logbook[[#This Row],[DGA (Azi)]]+INDEX(Logbook[CumDgaAzi],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="AZ6" s="27">
+      <c r="AZ6" s="101">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumCirc]),Logbook[[#This Row],[Circling]],Logbook[[#This Row],[Circling]]+INDEX(Logbook[CumCirc],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BA6" s="27">
+      <c r="BA6" s="101">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumTotalApps]),Logbook[[#This Row],[TotalApps]],Logbook[[#This Row],[TotalApps]]+INDEX(Logbook[CumTotalApps],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BB6" s="5">
+      <c r="BB6" s="25">
         <f>SUM(INDEX(Logbook[TotalHours],1):Logbook[[#This Row],[TotalHours]])</f>
         <v>0</v>
       </c>
-      <c r="BC6" s="28">
+      <c r="BC6" s="102">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[Cum2D]),SUM(Logbook[[#This Row],[VOR]:[DGA (Azi)]]),SUM(Logbook[[#This Row],[VOR]:[DGA (Azi)]])+INDEX(Logbook[Cum2D],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BD6" s="27">
+      <c r="BD6" s="101">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[Cum3D]),Logbook[[#This Row],[ILS]],Logbook[[#This Row],[ILS]]+INDEX(Logbook[Cum3D],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BE6" s="28">
+      <c r="BE6" s="102">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumCDI]),SUM(Logbook[[#This Row],[ILS]:[RNP]])+Logbook[[#This Row],[DGA (CDI)]],SUM(Logbook[[#This Row],[ILS]:[RNP]])+Logbook[[#This Row],[DGA (CDI)]]+INDEX(Logbook[CumCDI],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BF6" s="6">
+      <c r="BF6" s="103">
         <f>IF(ROW()-ROW(Logbook[#Headers])=ROWS(Logbook[CumAzi]),Logbook[[#This Row],[NDB]]+Logbook[[#This Row],[DGA (Azi)]],Logbook[[#This Row],[NDB]]+Logbook[[#This Row],[DGA (Azi)]]+INDEX(Logbook[CumAzi],ROW()-ROW(Logbook[#Headers])+1))</f>
         <v>0</v>
       </c>
-      <c r="BG6" s="21"/>
+      <c r="BG6" s="15"/>
       <c r="BM6"/>
       <c r="BN6"/>
       <c r="BO6"/>
@@ -6376,164 +6403,164 @@
       <c r="BU6"/>
       <c r="BV6"/>
     </row>
-    <row r="7" spans="1:74" s="22" customFormat="1" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:74" s="16" customFormat="1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A7"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55" t="s">
+      <c r="B7" s="104"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="56">
+      <c r="K7" s="49">
         <f>SUBTOTAL(109,Logbook[TotalHours])</f>
         <v>0</v>
       </c>
-      <c r="L7" s="57"/>
-      <c r="M7" s="58">
+      <c r="L7" s="50"/>
+      <c r="M7" s="51">
         <f>SUBTOTAL(109,Logbook[Custom 1])</f>
         <v>0</v>
       </c>
-      <c r="N7" s="58">
+      <c r="N7" s="51">
         <f>SUBTOTAL(109,Logbook[Custom 2])</f>
         <v>0</v>
       </c>
-      <c r="O7" s="58">
+      <c r="O7" s="51">
         <f>SUBTOTAL(109,Logbook[Custom 3])</f>
         <v>0</v>
       </c>
-      <c r="P7" s="59">
+      <c r="P7" s="52">
         <f>SUBTOTAL(109,Logbook[Custom 4])</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="58">
+      <c r="Q7" s="51">
         <f>SUBTOTAL(109,Logbook[SeIcusDay])</f>
         <v>0</v>
       </c>
-      <c r="R7" s="58">
+      <c r="R7" s="51">
         <f>SUBTOTAL(109,Logbook[SeIcusNight])</f>
         <v>0</v>
       </c>
-      <c r="S7" s="58">
+      <c r="S7" s="51">
         <f>SUBTOTAL(109,Logbook[SeDualDay])</f>
         <v>0</v>
       </c>
-      <c r="T7" s="58">
+      <c r="T7" s="51">
         <f>SUBTOTAL(109,Logbook[SeDualNight])</f>
         <v>0</v>
       </c>
-      <c r="U7" s="58">
+      <c r="U7" s="51">
         <f>SUBTOTAL(109,Logbook[SeCommandDay])</f>
         <v>0</v>
       </c>
-      <c r="V7" s="58">
+      <c r="V7" s="51">
         <f>SUBTOTAL(109,Logbook[SeCommandNight])</f>
         <v>0</v>
       </c>
-      <c r="W7" s="58">
+      <c r="W7" s="51">
         <f>SUBTOTAL(109,Logbook[MeIcusDay])</f>
         <v>0</v>
       </c>
-      <c r="X7" s="58">
+      <c r="X7" s="51">
         <f>SUBTOTAL(109,Logbook[MeIcusNight])</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="58">
+      <c r="Y7" s="51">
         <f>SUBTOTAL(109,Logbook[MeDualDay])</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="58">
+      <c r="Z7" s="51">
         <f>SUBTOTAL(109,Logbook[MeDualNight])</f>
         <v>0</v>
       </c>
-      <c r="AA7" s="58">
+      <c r="AA7" s="51">
         <f>SUBTOTAL(109,Logbook[MeCommandDay])</f>
         <v>0</v>
       </c>
-      <c r="AB7" s="58">
+      <c r="AB7" s="51">
         <f>SUBTOTAL(109,Logbook[MeCommandNight])</f>
         <v>0</v>
       </c>
-      <c r="AC7" s="58">
+      <c r="AC7" s="51">
         <f>SUBTOTAL(109,Logbook[CopilotDay])</f>
         <v>0</v>
       </c>
-      <c r="AD7" s="58">
+      <c r="AD7" s="51">
         <f>SUBTOTAL(109,Logbook[CopilotNight])</f>
         <v>0</v>
       </c>
-      <c r="AE7" s="58">
+      <c r="AE7" s="51">
         <f>SUBTOTAL(109,Logbook[IfrIf])</f>
         <v>0</v>
       </c>
-      <c r="AF7" s="58">
+      <c r="AF7" s="51">
         <f>SUBTOTAL(109,Logbook[IfrSim])</f>
         <v>0</v>
       </c>
-      <c r="AG7" s="59">
+      <c r="AG7" s="52">
         <f>SUBTOTAL(109,Logbook[LandingsDay])</f>
         <v>0</v>
       </c>
-      <c r="AH7" s="59">
+      <c r="AH7" s="52">
         <f>SUBTOTAL(109,Logbook[LandingsNight])</f>
         <v>0</v>
       </c>
-      <c r="AI7" s="59">
+      <c r="AI7" s="52">
         <f>SUBTOTAL(109,Logbook[ILS])</f>
         <v>0</v>
       </c>
-      <c r="AJ7" s="59">
+      <c r="AJ7" s="52">
         <f>SUBTOTAL(109,Logbook[VOR])</f>
         <v>0</v>
       </c>
-      <c r="AK7" s="59">
+      <c r="AK7" s="52">
         <f>SUBTOTAL(109,Logbook[RNP])</f>
         <v>0</v>
       </c>
-      <c r="AL7" s="59">
+      <c r="AL7" s="52">
         <f>SUBTOTAL(109,Logbook[NDB])</f>
         <v>0</v>
       </c>
-      <c r="AM7" s="59">
+      <c r="AM7" s="52">
         <f>SUBTOTAL(109,Logbook[DGA (CDI)])</f>
         <v>0</v>
       </c>
-      <c r="AN7" s="59">
+      <c r="AN7" s="52">
         <f>SUBTOTAL(109,Logbook[DGA (Azi)])</f>
         <v>0</v>
       </c>
-      <c r="AO7" s="59">
+      <c r="AO7" s="52">
         <f>SUBTOTAL(109,Logbook[Circling])</f>
         <v>0</v>
       </c>
-      <c r="AP7" s="60">
+      <c r="AP7" s="53">
         <f>SUBTOTAL(109,Logbook[TotalHours])</f>
         <v>0</v>
       </c>
-      <c r="AQ7" s="61">
+      <c r="AQ7" s="105">
         <f>SUBTOTAL(109,Logbook[TotalApps])</f>
         <v>0</v>
       </c>
-      <c r="AR7" s="62"/>
-      <c r="AS7" s="62"/>
-      <c r="AT7" s="62"/>
-      <c r="AU7" s="62"/>
-      <c r="AV7" s="62"/>
-      <c r="AW7" s="62"/>
-      <c r="AX7" s="62"/>
-      <c r="AY7" s="62"/>
-      <c r="AZ7" s="62"/>
-      <c r="BA7" s="63"/>
-      <c r="BB7" s="62"/>
-      <c r="BC7" s="62"/>
-      <c r="BD7" s="62"/>
-      <c r="BE7" s="62"/>
-      <c r="BF7" s="64"/>
-      <c r="BG7" s="21"/>
+      <c r="AR7" s="106"/>
+      <c r="AS7" s="106"/>
+      <c r="AT7" s="106"/>
+      <c r="AU7" s="106"/>
+      <c r="AV7" s="106"/>
+      <c r="AW7" s="106"/>
+      <c r="AX7" s="106"/>
+      <c r="AY7" s="106"/>
+      <c r="AZ7" s="106"/>
+      <c r="BA7" s="107"/>
+      <c r="BB7" s="106"/>
+      <c r="BC7" s="106"/>
+      <c r="BD7" s="106"/>
+      <c r="BE7" s="106"/>
+      <c r="BF7" s="108"/>
+      <c r="BG7" s="15"/>
       <c r="BM7"/>
       <c r="BN7"/>
       <c r="BO7"/>
@@ -6545,71 +6572,71 @@
       <c r="BU7"/>
       <c r="BV7"/>
     </row>
-    <row r="8" spans="1:74" s="43" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:74" s="37" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="68" t="s">
+      <c r="B8" s="109"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="114"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="69">
+      <c r="K8" s="57">
         <f>SUBTOTAL(109,Logbook[TotalHours])+SUBTOTAL(109,Logbook[IfrSim])</f>
         <v>0</v>
       </c>
-      <c r="L8" s="65"/>
-      <c r="M8" s="70"/>
-      <c r="N8" s="70"/>
-      <c r="O8" s="71"/>
-      <c r="P8" s="71"/>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="72"/>
-      <c r="T8" s="72"/>
-      <c r="U8" s="72"/>
-      <c r="V8" s="72"/>
-      <c r="W8" s="72"/>
-      <c r="X8" s="72"/>
-      <c r="Y8" s="72"/>
-      <c r="Z8" s="72"/>
-      <c r="AA8" s="72"/>
-      <c r="AB8" s="72"/>
-      <c r="AC8" s="72"/>
-      <c r="AD8" s="72"/>
-      <c r="AE8" s="72"/>
-      <c r="AF8" s="72"/>
-      <c r="AG8" s="36"/>
-      <c r="AH8" s="36"/>
-      <c r="AI8" s="36"/>
-      <c r="AJ8" s="36"/>
-      <c r="AK8" s="36"/>
-      <c r="AL8" s="36"/>
-      <c r="AM8" s="36"/>
-      <c r="AN8" s="36"/>
-      <c r="AO8" s="36"/>
-      <c r="AP8" s="73"/>
-      <c r="AQ8" s="74"/>
-      <c r="AR8" s="75"/>
-      <c r="AS8" s="75"/>
-      <c r="AT8" s="75"/>
-      <c r="AU8" s="75"/>
-      <c r="AV8" s="75"/>
-      <c r="AW8" s="75"/>
-      <c r="AX8" s="75"/>
-      <c r="AY8" s="75"/>
-      <c r="AZ8" s="75"/>
-      <c r="BA8" s="75"/>
-      <c r="BB8" s="75"/>
-      <c r="BC8" s="75"/>
-      <c r="BD8" s="75"/>
-      <c r="BE8" s="76"/>
-      <c r="BF8" s="75"/>
-      <c r="BG8" s="36"/>
+      <c r="L8" s="114"/>
+      <c r="M8" s="115"/>
+      <c r="N8" s="115"/>
+      <c r="O8" s="116"/>
+      <c r="P8" s="116"/>
+      <c r="Q8" s="117"/>
+      <c r="R8" s="117"/>
+      <c r="S8" s="117"/>
+      <c r="T8" s="117"/>
+      <c r="U8" s="117"/>
+      <c r="V8" s="117"/>
+      <c r="W8" s="117"/>
+      <c r="X8" s="117"/>
+      <c r="Y8" s="117"/>
+      <c r="Z8" s="117"/>
+      <c r="AA8" s="117"/>
+      <c r="AB8" s="117"/>
+      <c r="AC8" s="117"/>
+      <c r="AD8" s="117"/>
+      <c r="AE8" s="117"/>
+      <c r="AF8" s="117"/>
+      <c r="AG8" s="109"/>
+      <c r="AH8" s="109"/>
+      <c r="AI8" s="109"/>
+      <c r="AJ8" s="109"/>
+      <c r="AK8" s="109"/>
+      <c r="AL8" s="109"/>
+      <c r="AM8" s="109"/>
+      <c r="AN8" s="109"/>
+      <c r="AO8" s="109"/>
+      <c r="AP8" s="29"/>
+      <c r="AQ8" s="118"/>
+      <c r="AR8" s="28"/>
+      <c r="AS8" s="28"/>
+      <c r="AT8" s="28"/>
+      <c r="AU8" s="28"/>
+      <c r="AV8" s="28"/>
+      <c r="AW8" s="28"/>
+      <c r="AX8" s="28"/>
+      <c r="AY8" s="28"/>
+      <c r="AZ8" s="28"/>
+      <c r="BA8" s="28"/>
+      <c r="BB8" s="28"/>
+      <c r="BC8" s="28"/>
+      <c r="BD8" s="28"/>
+      <c r="BE8" s="119"/>
+      <c r="BF8" s="28"/>
+      <c r="BG8" s="30"/>
       <c r="BM8"/>
       <c r="BN8"/>
       <c r="BO8"/>
@@ -6621,7 +6648,7 @@
       <c r="BU8"/>
       <c r="BV8"/>
     </row>
-    <row r="9" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
@@ -6697,7 +6724,7 @@
       <c r="BU9"/>
       <c r="BV9"/>
     </row>
-    <row r="10" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="B10"/>
       <c r="C10"/>
@@ -6773,7 +6800,7 @@
       <c r="BU10"/>
       <c r="BV10"/>
     </row>
-    <row r="11" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="B11"/>
       <c r="C11"/>
@@ -6849,7 +6876,7 @@
       <c r="BU11"/>
       <c r="BV11"/>
     </row>
-    <row r="12" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="B12"/>
       <c r="C12"/>
@@ -6925,7 +6952,7 @@
       <c r="BU12"/>
       <c r="BV12"/>
     </row>
-    <row r="13" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="B13"/>
       <c r="C13"/>
@@ -7001,7 +7028,7 @@
       <c r="BU13"/>
       <c r="BV13"/>
     </row>
-    <row r="14" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="B14"/>
       <c r="C14"/>
@@ -7077,7 +7104,7 @@
       <c r="BU14"/>
       <c r="BV14"/>
     </row>
-    <row r="15" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A15"/>
       <c r="B15"/>
       <c r="C15"/>
@@ -7153,7 +7180,7 @@
       <c r="BU15"/>
       <c r="BV15"/>
     </row>
-    <row r="16" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
@@ -7229,7 +7256,7 @@
       <c r="BU16"/>
       <c r="BV16"/>
     </row>
-    <row r="17" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A17"/>
       <c r="B17"/>
       <c r="C17"/>
@@ -7305,7 +7332,7 @@
       <c r="BU17"/>
       <c r="BV17"/>
     </row>
-    <row r="18" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="B18"/>
       <c r="C18"/>
@@ -7381,7 +7408,7 @@
       <c r="BU18"/>
       <c r="BV18"/>
     </row>
-    <row r="19" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19"/>
@@ -7457,7 +7484,7 @@
       <c r="BU19"/>
       <c r="BV19"/>
     </row>
-    <row r="20" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="B20"/>
       <c r="C20"/>
@@ -7533,7 +7560,7 @@
       <c r="BU20"/>
       <c r="BV20"/>
     </row>
-    <row r="21" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
@@ -7609,7 +7636,7 @@
       <c r="BU21"/>
       <c r="BV21"/>
     </row>
-    <row r="22" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
@@ -7685,7 +7712,7 @@
       <c r="BU22"/>
       <c r="BV22"/>
     </row>
-    <row r="23" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
@@ -7761,7 +7788,7 @@
       <c r="BU23"/>
       <c r="BV23"/>
     </row>
-    <row r="24" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
@@ -7837,7 +7864,7 @@
       <c r="BU24"/>
       <c r="BV24"/>
     </row>
-    <row r="25" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="B25"/>
       <c r="C25"/>
@@ -7913,7 +7940,7 @@
       <c r="BU25"/>
       <c r="BV25"/>
     </row>
-    <row r="26" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="B26"/>
       <c r="C26"/>
@@ -7989,7 +8016,7 @@
       <c r="BU26"/>
       <c r="BV26"/>
     </row>
-    <row r="27" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="B27"/>
       <c r="C27"/>
@@ -8065,7 +8092,7 @@
       <c r="BU27"/>
       <c r="BV27"/>
     </row>
-    <row r="28" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="B28"/>
       <c r="C28"/>
@@ -8141,7 +8168,7 @@
       <c r="BU28"/>
       <c r="BV28"/>
     </row>
-    <row r="29" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="B29"/>
       <c r="C29"/>
@@ -8217,7 +8244,7 @@
       <c r="BU29"/>
       <c r="BV29"/>
     </row>
-    <row r="30" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="B30"/>
       <c r="C30"/>
@@ -8293,7 +8320,7 @@
       <c r="BU30"/>
       <c r="BV30"/>
     </row>
-    <row r="31" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A31"/>
       <c r="B31"/>
       <c r="C31"/>
@@ -8369,7 +8396,7 @@
       <c r="BU31"/>
       <c r="BV31"/>
     </row>
-    <row r="32" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A32"/>
       <c r="B32"/>
       <c r="C32"/>
@@ -8445,7 +8472,7 @@
       <c r="BU32"/>
       <c r="BV32"/>
     </row>
-    <row r="33" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A33"/>
       <c r="B33"/>
       <c r="C33"/>
@@ -8521,7 +8548,7 @@
       <c r="BU33"/>
       <c r="BV33"/>
     </row>
-    <row r="34" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="B34"/>
       <c r="C34"/>
@@ -8597,7 +8624,7 @@
       <c r="BU34"/>
       <c r="BV34"/>
     </row>
-    <row r="35" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="B35"/>
       <c r="C35"/>
@@ -8673,7 +8700,7 @@
       <c r="BU35"/>
       <c r="BV35"/>
     </row>
-    <row r="36" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="B36"/>
       <c r="C36"/>
@@ -8749,7 +8776,7 @@
       <c r="BU36"/>
       <c r="BV36"/>
     </row>
-    <row r="37" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="B37"/>
       <c r="C37"/>
@@ -8825,7 +8852,7 @@
       <c r="BU37"/>
       <c r="BV37"/>
     </row>
-    <row r="38" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="B38"/>
       <c r="C38"/>
@@ -8901,7 +8928,7 @@
       <c r="BU38"/>
       <c r="BV38"/>
     </row>
-    <row r="39" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="B39"/>
       <c r="C39"/>
@@ -8977,7 +9004,7 @@
       <c r="BU39"/>
       <c r="BV39"/>
     </row>
-    <row r="40" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="B40"/>
       <c r="C40"/>
@@ -9053,7 +9080,7 @@
       <c r="BU40"/>
       <c r="BV40"/>
     </row>
-    <row r="41" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="B41"/>
       <c r="C41"/>
@@ -9129,7 +9156,7 @@
       <c r="BU41"/>
       <c r="BV41"/>
     </row>
-    <row r="42" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="B42"/>
       <c r="C42"/>
@@ -9205,7 +9232,7 @@
       <c r="BU42"/>
       <c r="BV42"/>
     </row>
-    <row r="43" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43"/>
@@ -9281,7 +9308,7 @@
       <c r="BU43"/>
       <c r="BV43"/>
     </row>
-    <row r="44" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A44"/>
       <c r="B44"/>
       <c r="C44"/>
@@ -9357,7 +9384,7 @@
       <c r="BU44"/>
       <c r="BV44"/>
     </row>
-    <row r="45" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="B45"/>
       <c r="C45"/>
@@ -9433,7 +9460,7 @@
       <c r="BU45"/>
       <c r="BV45"/>
     </row>
-    <row r="46" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46"/>
@@ -9509,7 +9536,7 @@
       <c r="BU46"/>
       <c r="BV46"/>
     </row>
-    <row r="47" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="B47"/>
       <c r="C47"/>
@@ -9585,7 +9612,7 @@
       <c r="BU47"/>
       <c r="BV47"/>
     </row>
-    <row r="48" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="B48"/>
       <c r="C48"/>
@@ -9661,7 +9688,7 @@
       <c r="BU48"/>
       <c r="BV48"/>
     </row>
-    <row r="49" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="B49"/>
       <c r="C49"/>
@@ -9737,7 +9764,7 @@
       <c r="BU49"/>
       <c r="BV49"/>
     </row>
-    <row r="50" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="B50"/>
       <c r="C50"/>
@@ -9813,7 +9840,7 @@
       <c r="BU50"/>
       <c r="BV50"/>
     </row>
-    <row r="51" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="B51"/>
       <c r="C51"/>
@@ -9889,7 +9916,7 @@
       <c r="BU51"/>
       <c r="BV51"/>
     </row>
-    <row r="52" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="B52"/>
       <c r="C52"/>
@@ -9965,7 +9992,7 @@
       <c r="BU52"/>
       <c r="BV52"/>
     </row>
-    <row r="53" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="B53"/>
       <c r="C53"/>
@@ -10041,7 +10068,7 @@
       <c r="BU53"/>
       <c r="BV53"/>
     </row>
-    <row r="54" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="B54"/>
       <c r="C54"/>
@@ -10117,7 +10144,7 @@
       <c r="BU54"/>
       <c r="BV54"/>
     </row>
-    <row r="55" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A55"/>
       <c r="B55"/>
       <c r="C55"/>
@@ -10193,7 +10220,7 @@
       <c r="BU55"/>
       <c r="BV55"/>
     </row>
-    <row r="56" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A56"/>
       <c r="B56"/>
       <c r="C56"/>
@@ -10269,7 +10296,7 @@
       <c r="BU56"/>
       <c r="BV56"/>
     </row>
-    <row r="57" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="B57"/>
       <c r="C57"/>
@@ -10345,7 +10372,7 @@
       <c r="BU57"/>
       <c r="BV57"/>
     </row>
-    <row r="58" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="B58"/>
       <c r="C58"/>
@@ -10421,7 +10448,7 @@
       <c r="BU58"/>
       <c r="BV58"/>
     </row>
-    <row r="59" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="B59"/>
       <c r="C59"/>
@@ -10497,7 +10524,7 @@
       <c r="BU59"/>
       <c r="BV59"/>
     </row>
-    <row r="60" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="B60"/>
       <c r="C60"/>
@@ -10573,7 +10600,7 @@
       <c r="BU60"/>
       <c r="BV60"/>
     </row>
-    <row r="61" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="B61"/>
       <c r="C61"/>
@@ -10649,7 +10676,7 @@
       <c r="BU61"/>
       <c r="BV61"/>
     </row>
-    <row r="62" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A62"/>
       <c r="B62"/>
       <c r="C62"/>
@@ -10725,7 +10752,7 @@
       <c r="BU62"/>
       <c r="BV62"/>
     </row>
-    <row r="63" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="B63"/>
       <c r="C63"/>
@@ -10801,7 +10828,7 @@
       <c r="BU63"/>
       <c r="BV63"/>
     </row>
-    <row r="64" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="B64"/>
       <c r="C64"/>
@@ -10877,7 +10904,7 @@
       <c r="BU64"/>
       <c r="BV64"/>
     </row>
-    <row r="65" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="B65"/>
       <c r="C65"/>
@@ -10953,7 +10980,7 @@
       <c r="BU65"/>
       <c r="BV65"/>
     </row>
-    <row r="66" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="B66"/>
       <c r="C66"/>
@@ -11029,7 +11056,7 @@
       <c r="BU66"/>
       <c r="BV66"/>
     </row>
-    <row r="67" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="B67"/>
       <c r="C67"/>
@@ -11105,7 +11132,7 @@
       <c r="BU67"/>
       <c r="BV67"/>
     </row>
-    <row r="68" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="B68"/>
       <c r="C68"/>
@@ -11181,7 +11208,7 @@
       <c r="BU68"/>
       <c r="BV68"/>
     </row>
-    <row r="69" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="B69"/>
       <c r="C69"/>
@@ -11257,7 +11284,7 @@
       <c r="BU69"/>
       <c r="BV69"/>
     </row>
-    <row r="70" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="B70"/>
       <c r="C70"/>
@@ -11333,7 +11360,7 @@
       <c r="BU70"/>
       <c r="BV70"/>
     </row>
-    <row r="71" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="B71"/>
       <c r="C71"/>
@@ -11409,7 +11436,7 @@
       <c r="BU71"/>
       <c r="BV71"/>
     </row>
-    <row r="72" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="B72"/>
       <c r="C72"/>
@@ -11485,7 +11512,7 @@
       <c r="BU72"/>
       <c r="BV72"/>
     </row>
-    <row r="73" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="B73"/>
       <c r="C73"/>
@@ -11561,7 +11588,7 @@
       <c r="BU73"/>
       <c r="BV73"/>
     </row>
-    <row r="74" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="B74"/>
       <c r="C74"/>
@@ -11637,7 +11664,7 @@
       <c r="BU74"/>
       <c r="BV74"/>
     </row>
-    <row r="75" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="B75"/>
       <c r="C75"/>
@@ -11713,7 +11740,7 @@
       <c r="BU75"/>
       <c r="BV75"/>
     </row>
-    <row r="76" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="B76"/>
       <c r="C76"/>
@@ -11789,7 +11816,7 @@
       <c r="BU76"/>
       <c r="BV76"/>
     </row>
-    <row r="77" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="B77"/>
       <c r="C77"/>
@@ -11865,7 +11892,7 @@
       <c r="BU77"/>
       <c r="BV77"/>
     </row>
-    <row r="78" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A78"/>
       <c r="B78"/>
       <c r="C78"/>
@@ -11941,7 +11968,7 @@
       <c r="BU78"/>
       <c r="BV78"/>
     </row>
-    <row r="79" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A79"/>
       <c r="B79"/>
       <c r="C79"/>
@@ -12017,7 +12044,7 @@
       <c r="BU79"/>
       <c r="BV79"/>
     </row>
-    <row r="80" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A80"/>
       <c r="B80"/>
       <c r="C80"/>
@@ -12093,7 +12120,7 @@
       <c r="BU80"/>
       <c r="BV80"/>
     </row>
-    <row r="81" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="B81"/>
       <c r="C81"/>
@@ -12169,7 +12196,7 @@
       <c r="BU81"/>
       <c r="BV81"/>
     </row>
-    <row r="82" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="B82"/>
       <c r="C82"/>
@@ -12245,7 +12272,7 @@
       <c r="BU82"/>
       <c r="BV82"/>
     </row>
-    <row r="83" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="B83"/>
       <c r="C83"/>
@@ -12321,7 +12348,7 @@
       <c r="BU83"/>
       <c r="BV83"/>
     </row>
-    <row r="84" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="B84"/>
       <c r="C84"/>
@@ -12397,7 +12424,7 @@
       <c r="BU84"/>
       <c r="BV84"/>
     </row>
-    <row r="85" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="B85"/>
       <c r="C85"/>
@@ -12473,7 +12500,7 @@
       <c r="BU85"/>
       <c r="BV85"/>
     </row>
-    <row r="86" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="B86"/>
       <c r="C86"/>
@@ -12549,7 +12576,7 @@
       <c r="BU86"/>
       <c r="BV86"/>
     </row>
-    <row r="87" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="B87"/>
       <c r="C87"/>
@@ -12625,7 +12652,7 @@
       <c r="BU87"/>
       <c r="BV87"/>
     </row>
-    <row r="88" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A88"/>
       <c r="B88"/>
       <c r="C88"/>
@@ -12701,7 +12728,7 @@
       <c r="BU88"/>
       <c r="BV88"/>
     </row>
-    <row r="89" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="B89"/>
       <c r="C89"/>
@@ -12777,7 +12804,7 @@
       <c r="BU89"/>
       <c r="BV89"/>
     </row>
-    <row r="90" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="B90"/>
       <c r="C90"/>
@@ -12853,7 +12880,7 @@
       <c r="BU90"/>
       <c r="BV90"/>
     </row>
-    <row r="91" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="B91"/>
       <c r="C91"/>
@@ -12929,7 +12956,7 @@
       <c r="BU91"/>
       <c r="BV91"/>
     </row>
-    <row r="92" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="B92"/>
       <c r="C92"/>
@@ -13005,7 +13032,7 @@
       <c r="BU92"/>
       <c r="BV92"/>
     </row>
-    <row r="93" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="B93"/>
       <c r="C93"/>
@@ -13081,7 +13108,7 @@
       <c r="BU93"/>
       <c r="BV93"/>
     </row>
-    <row r="94" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="B94"/>
       <c r="C94"/>
@@ -13157,7 +13184,7 @@
       <c r="BU94"/>
       <c r="BV94"/>
     </row>
-    <row r="95" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="B95"/>
       <c r="C95"/>
@@ -13233,7 +13260,7 @@
       <c r="BU95"/>
       <c r="BV95"/>
     </row>
-    <row r="96" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="B96"/>
       <c r="C96"/>
@@ -13309,7 +13336,7 @@
       <c r="BU96"/>
       <c r="BV96"/>
     </row>
-    <row r="97" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="B97"/>
       <c r="C97"/>
@@ -13385,7 +13412,7 @@
       <c r="BU97"/>
       <c r="BV97"/>
     </row>
-    <row r="98" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A98"/>
       <c r="B98"/>
       <c r="C98"/>
@@ -13461,7 +13488,7 @@
       <c r="BU98"/>
       <c r="BV98"/>
     </row>
-    <row r="99" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="B99"/>
       <c r="C99"/>
@@ -13537,7 +13564,7 @@
       <c r="BU99"/>
       <c r="BV99"/>
     </row>
-    <row r="100" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="B100"/>
       <c r="C100"/>
@@ -13613,7 +13640,7 @@
       <c r="BU100"/>
       <c r="BV100"/>
     </row>
-    <row r="101" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="B101"/>
       <c r="C101"/>
@@ -13689,7 +13716,7 @@
       <c r="BU101"/>
       <c r="BV101"/>
     </row>
-    <row r="102" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="B102"/>
       <c r="C102"/>
@@ -13765,7 +13792,7 @@
       <c r="BU102"/>
       <c r="BV102"/>
     </row>
-    <row r="103" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="B103"/>
       <c r="C103"/>
@@ -13841,7 +13868,7 @@
       <c r="BU103"/>
       <c r="BV103"/>
     </row>
-    <row r="104" spans="1:74" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A104"/>
       <c r="B104"/>
       <c r="C104"/>
